--- a/human_validation/judge/kor/judge_D007_S001_P001__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D007_S001_P001__qwen3-235b_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,229 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 진료실에 오신 것을 환영합니다. 저는 [이름] 선생님입니다. 오늘 어떤 일로 오시게 되었는지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 그게, 요즘 일할 때 너무 느려져서 왔어요. 손이 꼭 풀 속에서 움직이는 것 같은 느낌이랄까요. 머리 섹션 나누는 것처럼 간단한 것도, 염색약 섞는 것도 이제는 한참 걸리고... 사람들도 제가 예전처럼 빠르지 않다는 걸 눈치채기 시작했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 기분이 가라앉거나 우울하다고 느끼신 적 있으세요? 아니면 평소에 즐기시던 것들에 흥미를 잃으신 적은요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네... 요즘은 거의 매일 아침에 일어나면 기분이 정말 가라앉아 있어요. 가슴에 뭔가 무겁고 답답한 슬픔이 있는 느낌인데, 그냥 '내가 계획했던 삶을 만들어가려고 애쓰는 게 무슨 의미가 있나' 싶은 생각만 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 취미 생활이나 친구들과 보내는 시간처럼 예전에 즐거워하시던 일들도 이제는 별다른 즐거움을 주지 않나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네. 예전엔 손님들이랑 이야기하는 것도 좋아하고 일할 때도 좀 밝은 편이었고, 신입 스타일리스트들이 필요할 때 도와주기도 했어요. 친구들이랑 등산도 다니고요. 근데 지금은 그냥 고개 숙이고 사람들을 피하게 돼요. 사람들이 싫어서 그런 건 아닌데, 그냥... 예전처럼 그 활기가 제 안에 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 이런 기분, 그러니까 슬픔이나 느려진 느낌, 흥미를 잃은 상태가 얼마나 오래되셨어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 한 1년 2개월 정도 된 것 같아요. 이 무거운 우울감이랑 느려진 느낌이... 그 기간 내내 거의 계속 있었던 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 지난 1년 동안 식욕이나 체중에 변화가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네, 식욕이 좀 이상해졌어요. 딱히 그러려던 게 아닌데 끼니를 거르게 되고, 밤이 되면 그날 커피 한 잔이랑 뭐 몇 입 먹은 게 다였다는 걸 깨닫곤 해요. 옷도 헐렁해졌고요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 평소보다 스스로가 부족하다고 느끼거나 자신을 더 많이 탓하게 되시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네. 계속 제가 다른 사람들한테 짐만 된다는 생각이 들어요. 기본적인 것들은 제가 알아서 해야 하는데, 돈 관리도 제대로 못 하고, 일도, 살롱에서의 평범한 책임들도 못 지키고 있으니까요. 지금 이런 일이 생기는 것도 제가 자초한 것 같은 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 주요우울장애 (D013); 지속성 우울장애 (D014) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 예전에도 이렇게 슬픔이나 흥미 상실이 몇 주 이상 지속된 적이 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 네... 그러니까, 예전에도 기분이 가라앉은 적은 있었는데 이번엔 좀 달라요. 거의 매일 아침 가슴에 무겁고 답답한 슬픔을 안고 일어나요. 제가 그리던 삶을 만들어가려고 애써봤자 의미가 없다는 느낌이 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 주요우울장애 (D013); 지속성 우울장애 (D014) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 지금 느끼시는 것과 비슷한 슬픔과 흥미 상실이 몇 주 이상 지속되었던 우울 삽화를 예전에 겪으신 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 네... 지금이랑 비슷한 느낌이에요. 거의 매일 아침 가슴에 무겁고 답답한 슬픔을 안고 일어나요. 제가 계획했던 삶을 만들려고 애쓰는 게 딱히 의미가 없다는 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 주요우울장애 (D013); 지속성 우울장애 (D014) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 지금 겪고 계신 이 슬픈 시기와 예전에 기분이 가라앉았던 시기 사이에, 다시 이런 상태가 되기 전에 적어도 두어 달 정도 확실히 괜찮아졌던 시기가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 잘 모르겠어요. 확실하게 두어 달 정도 완전히 괜찮았던 시기가 있었는지 기억이 잘 안 나요. 조금 더 잘 버텼던 시기는 있었던 것 같은데, 그걸 '확실히 좋아졌다'고 할 수 있을지는 모르겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 주요우울장애 (D013); 지속성 우울장애 (D014) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 지금 이전에, 적어도 두 달 정도 확실히 괜찮아지고 원래의 모습으로 돌아온 것 같은 시기가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 그렇게 말할 수 있을지 모르겠어요. 확실하게 두 달 동안 원래 제 모습으로 돌아왔다고 느낀 기억은 없어요. 조금 나았던 시기는 있었을지 몰라도, 완전히 괜찮았던 건 아니었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 주요우울장애 (D013); 지속성 우울장애 (D014) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>진단명: 조현정동장애 (우울형) (D007)
 인구통계: 성별 여성 / 나이 21 / 직업상태 hairdresser hairstylist or cosmetologist / 최종학력 전문학사
@@ -575,296 +789,47 @@
 증상 지속 기간: 1 year and 8 months
 추가 요건: psychotic_symptoms and depressive_episode occur concurrently, depressive_episode is present for the majority of the total duration of the active and residual portions of the illness (Criterion C), delusions_and_hallucinations occur for 2 or more weeks in the absence of a major mood episode (Criterion B)
 주호소 증상 코드: S028
-배경 서술: 데보라가 일하던 버클리의 미용실 경기가 나빠지면서 예약 시간이 줄어들었고, 미래에 부티크 살롱을 열기 위해 꾸준히 모아온 저축은 임대료와 면허 갱신비, 기본 생활비로 조금씩 사라져갔다. 이후 1년 8개월에 걸쳐 재정 통제력을 잃어가는 스트레스는 점차 고정된 피해망상, 생생한 환각 경험, 고객들과 등산 친구들로부터의 위축, 장기간의 우울 삽화, 식욕과 체중 변화, 느려진 작업 속도, 짐이 되고 있다는 죄책감, 염색 조제와 일정 관리에 대한 집중력 저하, 반복되는 죽음에 대한 생각과 겹쳐 나타났다. 한때 믿음직스러웠던 일상 루틴이 무너져 위생 관리에서 실수를 하고, 후배 직원 지도를 그만두었으며, 노인복지관에서의 자원봉사 미용 서비스도 취소하기 시작했다. 오랜 단골 고객이자 살롱 매니저가 지속적인 악화를 알아채고 긴급 외래 진료를 받을 수 있도록 도와준 뒤에야 그녀는 정신건강의학과 진료를 받게 되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 진료실에 오신 것을 환영합니다. 저는 [이름] 선생님입니다. 오늘 어떤 일로 오시게 되었는지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 그게, 요즘 일할 때 너무 느려져서 왔어요. 손이 꼭 풀 속에서 움직이는 것 같은 느낌이랄까요. 머리 섹션 나누는 것처럼 간단한 것도, 염색약 섞는 것도 이제는 한참 걸리고... 사람들도 제가 예전처럼 빠르지 않다는 걸 눈치채기 시작했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 기분이 가라앉거나 우울하다고 느끼신 적 있으세요? 아니면 평소에 즐기시던 것들에 흥미를 잃으신 적은요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네... 요즘은 거의 매일 아침에 일어나면 기분이 정말 가라앉아 있어요. 가슴에 뭔가 무겁고 답답한 슬픔이 있는 느낌인데, 그냥 '내가 계획했던 삶을 만들어가려고 애쓰는 게 무슨 의미가 있나' 싶은 생각만 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 취미 생활이나 친구들과 보내는 시간처럼 예전에 즐거워하시던 일들도 이제는 별다른 즐거움을 주지 않나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네. 예전엔 손님들이랑 이야기하는 것도 좋아하고 일할 때도 좀 밝은 편이었고, 신입 스타일리스트들이 필요할 때 도와주기도 했어요. 친구들이랑 등산도 다니고요. 근데 지금은 그냥 고개 숙이고 사람들을 피하게 돼요. 사람들이 싫어서 그런 건 아닌데, 그냥... 예전처럼 그 활기가 제 안에 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 이런 기분, 그러니까 슬픔이나 느려진 느낌, 흥미를 잃은 상태가 얼마나 오래되셨어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 한 1년 2개월 정도 된 것 같아요. 이 무거운 우울감이랑 느려진 느낌이... 그 기간 내내 거의 계속 있었던 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 지난 1년 동안 식욕이나 체중에 변화가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네, 식욕이 좀 이상해졌어요. 딱히 그러려던 게 아닌데 끼니를 거르게 되고, 밤이 되면 그날 커피 한 잔이랑 뭐 몇 입 먹은 게 다였다는 걸 깨닫곤 해요. 옷도 헐렁해졌고요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 평소보다 스스로가 부족하다고 느끼거나 자신을 더 많이 탓하게 되시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네. 계속 제가 다른 사람들한테 짐만 된다는 생각이 들어요. 기본적인 것들은 제가 알아서 해야 하는데, 돈 관리도 제대로 못 하고, 일도, 살롱에서의 평범한 책임들도 못 지키고 있으니까요. 지금 이런 일이 생기는 것도 제가 자초한 것 같은 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 주요우울장애 (D013); 지속성 우울장애 (D014) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 예전에도 이렇게 슬픔이나 흥미 상실이 몇 주 이상 지속된 적이 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 네... 그러니까, 예전에도 기분이 가라앉은 적은 있었는데 이번엔 좀 달라요. 거의 매일 아침 가슴에 무겁고 답답한 슬픔을 안고 일어나요. 제가 그리던 삶을 만들어가려고 애써봤자 의미가 없다는 느낌이 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 고확률: 주요우울장애 (D013); 지속성 우울장애 (D014) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 지금 느끼시는 것과 비슷한 슬픔과 흥미 상실이 몇 주 이상 지속되었던 우울 삽화를 예전에 겪으신 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 네... 지금이랑 비슷한 느낌이에요. 거의 매일 아침 가슴에 무겁고 답답한 슬픔을 안고 일어나요. 제가 계획했던 삶을 만들려고 애쓰는 게 딱히 의미가 없다는 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 주요우울장애 (D013); 지속성 우울장애 (D014) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 지금 겪고 계신 이 슬픈 시기와 예전에 기분이 가라앉았던 시기 사이에, 다시 이런 상태가 되기 전에 적어도 두어 달 정도 확실히 괜찮아졌던 시기가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 잘 모르겠어요. 확실하게 두어 달 정도 완전히 괜찮았던 시기가 있었는지 기억이 잘 안 나요. 조금 더 잘 버텼던 시기는 있었던 것 같은데, 그걸 '확실히 좋아졌다'고 할 수 있을지는 모르겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 고확률: 주요우울장애 (D013); 지속성 우울장애 (D014) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 지금 이전에, 적어도 두 달 정도 확실히 괜찮아지고 원래의 모습으로 돌아온 것 같은 시기가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 그렇게 말할 수 있을지 모르겠어요. 확실하게 두 달 동안 원래 제 모습으로 돌아왔다고 느낀 기억은 없어요. 조금 나았던 시기는 있었을지 몰라도, 완전히 괜찮았던 건 아니었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
+배경 서술: 데보라가 일하던 버클리의 미용실 경기가 나빠지면서 예약 시간이 줄어들었고, 미래에 부티크 살롱을 열기 위해 꾸준히 모아온 저축은 임대료와 면허 갱신비, 기본 생활비로 조금씩 사라져갔다. 이후 1년 8개월에 걸쳐 재정 통제력을 잃어가는 스트레스는 점차 고정된 피해망상, 생생한 환각 경험, 고객들과 등산 친구들로부터의 위축, 장기간의 우울 삽화, 식욕과 체중 변화, 느려진 작업 속도, 짐이 되고 있다는 죄책감, 염색 조제와 일정 관리에 대한 집중력 저하, 반복되는 죽음에 대한 생각과 겹쳐 나타났다. 한때 믿음직스러웠던 일상 루틴이 무너져 위생 관리에서 실수를 하고, 후배 직원 지도를 그만두었으며, 노인복지관에서의 자원봉사 미용 서비스도 취소하기 시작했다. 오랜 단골 고객이자 살롱 매니저가 지속적인 악화를 알아채고 긴급 외래 진료를 받을 수 있도록 도와준 뒤에야 그녀는 정신건강의학과 진료를 받게 되었다.
+표집된 증상 목록:
+  - S019 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - S020 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
+  - S023 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.
+  - S024 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - S026 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - S028 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.
+  - S030 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+  - S031 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.
+  - S032 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
+        </is>
+      </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>[10번째 턴 · 의사의 감별진단] 고확률: 주요우울장애 (D013); 지속성 우울장애 (D014) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F33.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: psychotic_symptoms (관계=must_include, 요구개수=2, 충족개수=1, 커버리지=0.5)
-  확인된 근거: 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.
-  누락: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.; 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.; 와해된 사고/언어: 논리적이고 일관된 흐름이 부족해 말이나 생각이 흩어지고 따라가기 어려운 증상.; 와해된/비정상적 행동: 행동과 운동 조절이 심각하게 손상되어 상황에 맞지 않는 움직임이나 반응으로 나타나는 상태.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=5, 커버리지=1.0)
-  확인된 근거: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
-  누락: 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.; 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.</t>
+          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F33.2)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: 없음
+체크리스트 그룹: psychotic_symptoms (관계=must_include, 요구개수=2, 충족개수=1, 커버리지=0.5)
+확인된 근거:
+  - 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.
+체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=5, 커버리지=1.0)
+확인된 근거:
+  - 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.
+  - 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A46:B46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D007_S001_P001__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D007_S001_P001__qwen3-235b_kor.xlsx
@@ -775,6 +775,11 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -825,11 +830,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A46:B46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D007_S001_P001__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D007_S001_P001__qwen3-235b_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.105</v>
+        <v>0.2316</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.1068</v>
+        <v>0.2366</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.5833</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
